--- a/314e-ig/output/StructureDefinition-devicerequest-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-devicerequest-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-devicerequest-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-devicerequest-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-devicerequest-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-devicerequest-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-devicerequest-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-devicerequest-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -563,7 +563,7 @@
     <t>DeviceRequest.basedOn</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource|4.0.1) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/devicerequest-314e|http://314e.com/fhir/StructureDefinition/account-314e|http://314e.com/fhir/StructureDefinition/allergyintolerance-314e|http://314e.com/fhir/StructureDefinition/appointment-314e|http://314e.com/fhir/StructureDefinition/careplan-314e|http://314e.com/fhir/StructureDefinition/careteam-314e|http://314e.com/fhir/StructureDefinition/clinicalimpression-314e|http://314e.com/fhir/StructureDefinition/communicationrequest-314e|http://314e.com/fhir/StructureDefinition/condition-314e|http://314e.com/fhir/StructureDefinition/condition-diagnosis-314e|http://314e.com/fhir/StructureDefinition/condition-problem-healthconcern-314e|http://314e.com/fhir/StructureDefinition/contract-314e|http://314e.com/fhir/StructureDefinition/coverage-314e|http://314e.com/fhir/StructureDefinition/detectedissue-314e|http://314e.com/fhir/StructureDefinition/device-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-lab-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-notereport-314e|http://314e.com/fhir/StructureDefinition/documentreference-314e|http://314e.com/fhir/StructureDefinition/encounter-314e|http://314e.com/fhir/StructureDefinition/endpoint-314e|http://314e.com/fhir/StructureDefinition/episodeofcare-314e|http://314e.com/fhir/StructureDefinition/goal-314e|http://314e.com/fhir/StructureDefinition/group-314e|http://314e.com/fhir/StructureDefinition/healthcareservice-314e|http://314e.com/fhir/StructureDefinition/imagingstudy-314e|http://314e.com/fhir/StructureDefinition/immunization-314e|http://314e.com/fhir/StructureDefinition/immunizationevaluation-314e|http://314e.com/fhir/StructureDefinition/immunizationrecommendation-314e|http://314e.com/fhir/StructureDefinition/location-314e|http://314e.com/fhir/StructureDefinition/media-314e|http://314e.com/fhir/StructureDefinition/medication-314e|http://314e.com/fhir/StructureDefinition/medicationadministration-314e|http://314e.com/fhir/StructureDefinition/medicationdispense-314e|http://314e.com/fhir/StructureDefinition/medicationrequest-314e|http://314e.com/fhir/StructureDefinition/molecularsequence-314e|http://314e.com/fhir/StructureDefinition/nutritionorder-314e|http://314e.com/fhir/StructureDefinition/observation-314e|http://314e.com/fhir/StructureDefinition/observation-antimicrobial-susceptibility-314e|http://314e.com/fhir/StructureDefinition/observation-lab-general-314e|http://314e.com/fhir/StructureDefinition/observation-microbiology-314e|http://314e.com/fhir/StructureDefinition/observation-microorganism-314e|http://314e.com/fhir/StructureDefinition/organization-314e|http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e|http://314e.com/fhir/StructureDefinition/procedure-314e|http://314e.com/fhir/StructureDefinition/questionnaireresponse-314e|http://314e.com/fhir/StructureDefinition/relatedperson-314e|http://314e.com/fhir/StructureDefinition/requestgroup-314e|http://314e.com/fhir/StructureDefinition/schedule-314e|http://314e.com/fhir/StructureDefinition/servicerequest-314e|http://314e.com/fhir/StructureDefinition/slot-314e|http://314e.com/fhir/StructureDefinition/specimen-314e|http://314e.com/fhir/StructureDefinition/substance-314e|http://314e.com/fhir/StructureDefinition/task-314e|http://314e.com/fhir/StructureDefinition/visionprescription-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -714,7 +714,7 @@
     <t>DeviceRequest.code[x]</t>
   </si>
   <si>
-    <t>Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-device) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t>Reference(http://314e.com/fhir/StructureDefinition/device-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 CodeableConcept {http://314e.com/fhir/ig/StructureDefinition/codeableconcept-314e}</t>
   </si>
   <si>
@@ -986,7 +986,7 @@
     <t>DeviceRequest.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-patient) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/patient-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1014,7 +1014,7 @@
     <t>DeviceRequest.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|4.0.1) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/encounter-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1098,7 +1098,7 @@
     <t>DeviceRequest.requester</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e|http://314e.com/fhir/StructureDefinition/organization-314e|http://314e.com/fhir/StructureDefinition/device-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1150,7 +1150,7 @@
     <t>DeviceRequest.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1|HealthcareService|4.0.1|Patient|4.0.1|Device|4.0.1|RelatedPerson|4.0.1) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e|http://314e.com/fhir/StructureDefinition/organization-314e|http://314e.com/fhir/StructureDefinition/careteam-314e|http://314e.com/fhir/StructureDefinition/healthcareservice-314e|http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/device-314e|http://314e.com/fhir/StructureDefinition/relatedperson-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1199,7 +1199,7 @@
     <t>DeviceRequest.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1|DocumentReference|4.0.1) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/condition-314e|http://314e.com/fhir/StructureDefinition/condition-diagnosis-314e|http://314e.com/fhir/StructureDefinition/condition-problem-healthconcern-314e|http://314e.com/fhir/StructureDefinition/observation-314e|http://314e.com/fhir/StructureDefinition/observation-lab-general-314e|http://314e.com/fhir/StructureDefinition/observation-microbiology-314e|http://314e.com/fhir/StructureDefinition/observation-microorganism-314e|http://314e.com/fhir/StructureDefinition/observation-antimicrobial-susceptibility-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-lab-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-notereport-314e|http://314e.com/fhir/StructureDefinition/documentreference-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1215,7 +1215,7 @@
     <t>DeviceRequest.insurance</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Coverage|4.0.1|ClaimResponse|4.0.1) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/coverage-314e|ClaimResponse) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1283,7 +1283,7 @@
     <t>DeviceRequest.relevantHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance|4.0.1) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(Provenance) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1616,7 +1616,7 @@
     <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="181.94140625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/314e-ig/output/StructureDefinition-devicerequest-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-devicerequest-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-devicerequest-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-devicerequest-314e.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1829" uniqueCount="418">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -451,6 +451,27 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
+    <t>DeviceRequest.extension:cosigner</t>
+  </si>
+  <si>
+    <t>cosigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/resource-cosigner}
+</t>
+  </si>
+  <si>
+    <t>Individual who co-signed or verified this device request</t>
+  </si>
+  <si>
+    <t>Identifies an individual who reviewed, verified, or co-signed the associated
+clinical document, note, order, or healthcare record, alongside the primary author or requester.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t>DeviceRequest.extension:additionalInfo</t>
   </si>
   <si>
@@ -467,10 +488,6 @@
     <t>Applied at the root level of any resource. Used to capture supplementary
 or non-standard information related to a FHIR resource that is not
 represented by the core FHIR elements or existing profiles.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
   </si>
   <si>
     <t>DeviceRequest.modifierExtension</t>
@@ -1603,7 +1620,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO48"/>
+  <dimension ref="A1:AO49"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="56.9140625" customWidth="true" bestFit="true"/>
@@ -2719,7 +2736,7 @@
         <v>78</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>20</v>
@@ -2823,9 +2840,11 @@
         <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="C11" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="D11" t="s" s="2">
         <v>20</v>
       </c>
@@ -2840,19 +2859,19 @@
         <v>20</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2891,17 +2910,19 @@
         <v>20</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AC11" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC11" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>137</v>
+        <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2910,7 +2931,7 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>20</v>
+        <v>145</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>139</v>
@@ -2933,14 +2954,12 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
         <v>20</v>
       </c>
@@ -2949,7 +2968,7 @@
         <v>78</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>20</v>
@@ -2961,10 +2980,10 @@
         <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="M12" t="s" s="2">
         <v>135</v>
@@ -3006,19 +3025,17 @@
         <v>20</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="AC12" s="2"/>
       <c r="AD12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>20</v>
+        <v>137</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3027,7 +3044,7 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>145</v>
+        <v>20</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>139</v>
@@ -3050,12 +3067,14 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="D13" t="s" s="2">
         <v>20</v>
       </c>
@@ -3064,25 +3083,25 @@
         <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3142,33 +3161,33 @@
         <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>20</v>
+        <v>145</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>156</v>
+        <v>20</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>157</v>
+        <v>20</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>158</v>
+        <v>20</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>159</v>
+        <v>20</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>160</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3191,17 +3210,15 @@
         <v>89</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>165</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>20</v>
@@ -3250,7 +3267,7 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3265,27 +3282,27 @@
         <v>100</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>20</v>
+        <v>164</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>20</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3308,16 +3325,16 @@
         <v>89</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>102</v>
+        <v>167</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3367,7 +3384,7 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3382,13 +3399,13 @@
         <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AM15" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>20</v>
@@ -3425,15 +3442,17 @@
         <v>89</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>20</v>
@@ -3500,24 +3519,24 @@
         <v>178</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>181</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3540,13 +3559,13 @@
         <v>89</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3597,7 +3616,7 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3612,27 +3631,27 @@
         <v>100</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO17" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>20</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3643,7 +3662,7 @@
         <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>20</v>
@@ -3655,13 +3674,13 @@
         <v>89</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>190</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3712,13 +3731,13 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
@@ -3727,13 +3746,13 @@
         <v>100</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AL18" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="AL18" t="s" s="2">
+      <c r="AM18" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>20</v>
@@ -3744,10 +3763,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3764,23 +3783,21 @@
         <v>20</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>108</v>
+        <v>158</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="M19" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>197</v>
-      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>20</v>
@@ -3805,13 +3822,13 @@
         <v>20</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>199</v>
+        <v>20</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>20</v>
@@ -3829,7 +3846,7 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3844,27 +3861,27 @@
         <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>204</v>
+        <v>20</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>205</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3872,7 +3889,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>88</v>
@@ -3890,12 +3907,14 @@
         <v>108</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>20</v>
@@ -3920,13 +3939,13 @@
         <v>20</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>20</v>
@@ -3944,10 +3963,10 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>88</v>
@@ -3959,27 +3978,27 @@
         <v>100</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>131</v>
+        <v>207</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>20</v>
+        <v>210</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3987,7 +4006,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>88</v>
@@ -3996,7 +4015,7 @@
         <v>20</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>89</v>
@@ -4005,19 +4024,17 @@
         <v>108</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q21" t="s" s="2">
-        <v>217</v>
-      </c>
+      <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
         <v>20</v>
       </c>
@@ -4037,13 +4054,13 @@
         <v>20</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>20</v>
@@ -4061,10 +4078,10 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>88</v>
@@ -4076,16 +4093,16 @@
         <v>100</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>221</v>
+        <v>131</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>20</v>
@@ -4093,10 +4110,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4104,7 +4121,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>88</v>
@@ -4119,20 +4136,22 @@
         <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>225</v>
+        <v>108</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q22" s="2"/>
+      <c r="Q22" t="s" s="2">
+        <v>222</v>
+      </c>
       <c r="R22" t="s" s="2">
         <v>20</v>
       </c>
@@ -4152,72 +4171,74 @@
         <v>20</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="Y22" s="2"/>
+        <v>203</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="Z22" t="s" s="2">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="AC22" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>230</v>
+        <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>88</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>231</v>
+        <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>167</v>
+        <v>226</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>235</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="C23" t="s" s="2">
-        <v>237</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>88</v>
@@ -4232,13 +4253,13 @@
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4265,31 +4286,27 @@
         <v>20</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y23" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>20</v>
+        <v>233</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>20</v>
+        <v>235</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>88</v>
@@ -4298,36 +4315,36 @@
         <v>88</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>20</v>
+        <v>236</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>20</v>
@@ -4349,13 +4366,13 @@
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4382,13 +4399,13 @@
         <v>20</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>243</v>
+        <v>20</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>244</v>
+        <v>20</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>245</v>
+        <v>20</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>20</v>
@@ -4406,7 +4423,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>88</v>
@@ -4421,29 +4438,31 @@
         <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="C25" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="B25" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>20</v>
       </c>
@@ -4461,16 +4480,16 @@
         <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4497,13 +4516,13 @@
         <v>20</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>20</v>
+        <v>248</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>20</v>
+        <v>249</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>20</v>
@@ -4521,10 +4540,10 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>88</v>
@@ -4533,41 +4552,41 @@
         <v>20</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>20</v>
+        <v>237</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>20</v>
+        <v>172</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>20</v>
+        <v>239</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>20</v>
+        <v>240</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>255</v>
+        <v>20</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>20</v>
@@ -4579,17 +4598,15 @@
         <v>20</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>133</v>
+        <v>253</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>258</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -4626,31 +4643,31 @@
         <v>20</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>136</v>
+        <v>20</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>259</v>
+        <v>20</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>137</v>
+        <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>139</v>
+        <v>20</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>20</v>
@@ -4659,7 +4676,7 @@
         <v>20</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>20</v>
@@ -4670,23 +4687,21 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="C27" t="s" s="2">
-        <v>262</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>20</v>
+        <v>260</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>20</v>
@@ -4698,16 +4713,16 @@
         <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4745,19 +4760,19 @@
         <v>20</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>20</v>
+        <v>136</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>20</v>
+        <v>264</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>20</v>
+        <v>137</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4766,7 +4781,7 @@
         <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>231</v>
+        <v>20</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>139</v>
@@ -4775,10 +4790,10 @@
         <v>20</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>267</v>
+        <v>20</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>20</v>
@@ -4789,12 +4804,14 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="C28" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="D28" t="s" s="2">
         <v>20</v>
       </c>
@@ -4803,7 +4820,7 @@
         <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>20</v>
@@ -4812,23 +4829,21 @@
         <v>20</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="N28" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="L28" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>275</v>
-      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>20</v>
       </c>
@@ -4876,7 +4891,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4885,19 +4900,19 @@
         <v>79</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>20</v>
+        <v>236</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>20</v>
@@ -4908,10 +4923,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4922,7 +4937,7 @@
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
@@ -4934,19 +4949,19 @@
         <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -4995,13 +5010,13 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
@@ -5013,10 +5028,10 @@
         <v>20</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>20</v>
@@ -5027,10 +5042,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5041,7 +5056,7 @@
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>20</v>
@@ -5050,19 +5065,23 @@
         <v>20</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="O30" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="L30" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>20</v>
       </c>
@@ -5110,13 +5129,13 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
@@ -5128,24 +5147,24 @@
         <v>20</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>167</v>
+        <v>291</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>233</v>
+        <v>292</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>234</v>
+        <v>20</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>235</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5156,7 +5175,7 @@
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>20</v>
@@ -5168,13 +5187,13 @@
         <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>248</v>
+        <v>294</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>249</v>
+        <v>295</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>250</v>
+        <v>296</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5225,53 +5244,53 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>251</v>
+        <v>293</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>20</v>
+        <v>172</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>20</v>
+        <v>239</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>20</v>
+        <v>240</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>255</v>
+        <v>20</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>20</v>
@@ -5283,17 +5302,15 @@
         <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>133</v>
+        <v>253</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>258</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -5342,19 +5359,19 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>139</v>
+        <v>20</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>20</v>
@@ -5363,7 +5380,7 @@
         <v>20</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>20</v>
@@ -5374,14 +5391,14 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>295</v>
+        <v>260</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5394,26 +5411,24 @@
         <v>20</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
         <v>133</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>296</v>
+        <v>261</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>297</v>
+        <v>262</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>298</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>20</v>
       </c>
@@ -5461,7 +5476,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>299</v>
+        <v>265</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5482,7 +5497,7 @@
         <v>20</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>131</v>
+        <v>257</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>20</v>
@@ -5493,42 +5508,46 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="O34" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>20</v>
       </c>
@@ -5552,58 +5571,58 @@
         <v>20</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>243</v>
+        <v>20</v>
       </c>
       <c r="Y34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF34" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="Z34" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>300</v>
-      </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>167</v>
+        <v>20</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>233</v>
+        <v>131</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>234</v>
+        <v>20</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>235</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35">
@@ -5642,9 +5661,7 @@
       <c r="M35" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="N35" t="s" s="2">
-        <v>309</v>
-      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -5669,10 +5686,10 @@
         <v>20</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>20</v>
+        <v>248</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>20</v>
+        <v>309</v>
       </c>
       <c r="Z35" t="s" s="2">
         <v>20</v>
@@ -5711,16 +5728,16 @@
         <v>20</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="36">
@@ -5736,7 +5753,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>88</v>
@@ -5748,7 +5765,7 @@
         <v>20</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
         <v>311</v>
@@ -5759,7 +5776,9 @@
       <c r="M36" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="N36" s="2"/>
+      <c r="N36" t="s" s="2">
+        <v>314</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -5811,7 +5830,7 @@
         <v>310</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>88</v>
@@ -5823,27 +5842,27 @@
         <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>314</v>
+        <v>20</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>315</v>
+        <v>172</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>316</v>
+        <v>238</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>317</v>
+        <v>239</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>318</v>
+        <v>240</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5851,7 +5870,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>88</v>
@@ -5866,13 +5885,13 @@
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5923,10 +5942,10 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>88</v>
@@ -5938,27 +5957,27 @@
         <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AO37" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>327</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5981,13 +6000,13 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6038,7 +6057,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6053,27 +6072,27 @@
         <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AO38" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>336</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6096,13 +6115,13 @@
         <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6153,7 +6172,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6168,27 +6187,27 @@
         <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AO39" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>345</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6211,13 +6230,13 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6268,7 +6287,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6283,27 +6302,27 @@
         <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AO40" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="AO40" t="s" s="2">
-        <v>20</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6326,13 +6345,13 @@
         <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>301</v>
+        <v>352</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6359,13 +6378,13 @@
         <v>20</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>243</v>
+        <v>20</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>357</v>
+        <v>20</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>358</v>
+        <v>20</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>20</v>
@@ -6383,7 +6402,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6398,16 +6417,16 @@
         <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>20</v>
@@ -6415,10 +6434,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6441,13 +6460,13 @@
         <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>364</v>
+        <v>306</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6474,13 +6493,13 @@
         <v>20</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>20</v>
+        <v>248</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>20</v>
+        <v>362</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>20</v>
+        <v>363</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>20</v>
@@ -6498,7 +6517,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6513,16 +6532,16 @@
         <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="AL42" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>20</v>
@@ -6530,10 +6549,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6544,7 +6563,7 @@
         <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>20</v>
@@ -6556,7 +6575,7 @@
         <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>301</v>
+        <v>369</v>
       </c>
       <c r="L43" t="s" s="2">
         <v>370</v>
@@ -6589,13 +6608,13 @@
         <v>20</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>243</v>
+        <v>20</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>372</v>
+        <v>20</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>373</v>
+        <v>20</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>20</v>
@@ -6613,13 +6632,13 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>20</v>
@@ -6628,27 +6647,27 @@
         <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>378</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6671,13 +6690,13 @@
         <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>380</v>
+        <v>306</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6704,13 +6723,13 @@
         <v>20</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>20</v>
+        <v>248</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>20</v>
+        <v>377</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>20</v>
+        <v>378</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>20</v>
@@ -6728,7 +6747,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6743,19 +6762,19 @@
         <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="AL44" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="AM44" t="s" s="2">
+      <c r="AO44" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>20</v>
       </c>
     </row>
     <row r="45">
@@ -6783,7 +6802,7 @@
         <v>20</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
         <v>385</v>
@@ -6792,7 +6811,7 @@
         <v>386</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6858,16 +6877,16 @@
         <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AM45" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="AL45" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>390</v>
-      </c>
       <c r="AN45" t="s" s="2">
-        <v>20</v>
+        <v>382</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>20</v>
@@ -6875,10 +6894,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6901,18 +6920,16 @@
         <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>175</v>
+        <v>390</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="M46" t="s" s="2">
-        <v>393</v>
-      </c>
       <c r="N46" s="2"/>
-      <c r="O46" t="s" s="2">
-        <v>394</v>
-      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>20</v>
       </c>
@@ -6960,7 +6977,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6975,13 +6992,13 @@
         <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>20</v>
@@ -6992,10 +7009,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7018,16 +7035,18 @@
         <v>20</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="L47" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>20</v>
       </c>
@@ -7075,7 +7094,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7090,27 +7109,27 @@
         <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AM47" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AL47" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>404</v>
-      </c>
       <c r="AN47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>405</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7133,17 +7152,15 @@
         <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>410</v>
-      </c>
+        <v>406</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>20</v>
@@ -7192,7 +7209,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7207,18 +7224,135 @@
         <v>100</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO48" t="s" s="2">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="AL48" t="s" s="2">
+      <c r="B49" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="O49" s="2"/>
+      <c r="P49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AL49" t="s" s="2">
         <v>131</v>
       </c>
-      <c r="AM48" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO48" t="s" s="2">
+      <c r="AM49" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO49" t="s" s="2">
         <v>20</v>
       </c>
     </row>
